--- a/data_extactor/batch_10_fa/trimmed/batch_0006_fa_trim.xlsx
+++ b/data_extactor/batch_10_fa/trimmed/batch_0006_fa_trim.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | نظارت | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | آموزش و تدریس | مدیریت و امور اداری | بازاریابی و فروش | امور اداری و منابع انسانی | روان‌شناسی</t>
+          <t>خدمات مشتری و شخصی | آموزش و پرورش | مدیریت و اداره | فروش و بازاریابی | پرسنل و منابع انسانی | روان‌شناسی</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | استدلال قیاسی | درک کتبی | بیان کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کارشناسان و متخصصان تغذیه | فیزیولوژیست‌های ورزشی | مربیان ورزشی و مربیان آمادگی جسمانی گروهی | کارشناسان آموزش بهداشت | کارکنان امور اوقات فراغت و تفریحات | مدرسان دانشگاهی تربیت‌بدنی و علوم ورزشی | مدیران مراکز آب‌درمانی و اسپا</t>
+          <t>کارشناسان و متخصصان تغذیه و رژیم‌درمانی | فیزیولوژیست‌های ورزشی | مربیان ورزش و آمادگی جسمانی گروهی | کارشناسان آموزش بهداشت و ارتقای سلامت | کارکنان و متصدیان امور تفریحی و اوقات فراغت | مدرسان علوم ورزشی، تربیت بدنی و اوقات فراغت در آموزش عالی | مدیران مراکز خدمات اسپا و مراقبت‌های زیبایی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی و تدوین دوره‌ها و برنامه‌های ورزشی و ارتقای تندرستی عموم | نیازسنجی و ارزیابی اثربخشی برنامه‌ها و دوره‌های تندرستی | نظارت بر نگهداری، ایمنی و بهداشت تجهیزات و امکانات ورزشی | مدیریت و راهبری مربیان ورزشی و کارشناسان سلامت و تغذیه | برگزاری دوره‌ها و کارگاه‌های آموزشی برای کارکنان و مربیان | آموزش و نمایش شیوه صحیح کار با دستگاه‌ها و ادوات ورزشی | برنامه‌ریزی غربالگری‌های سلامت و اقدامات پیشگیرانه پزشکی | نظارت بر رویدادها، همایش‌های ورزشی و پویش‌های ارتقای سلامت | تدوین بودجه‌های عملیاتی و پایش هزینه‌های برنامه‌های ورزشی | ارائه مشاوره‌ها و راهنمایی‌های فردی در حوزه سبک زندگی سالم</t>
+          <t>انجام نیازسنجی یا نظرسنجی برای تعیین میزان علاقه به برنامه‌ها، رویدادها یا خدمات سلامتی و تناسب اندام، یا رضایت از آن‌ها. | برگزاری یا تسهیل دوره‌های آموزشی یا سمینارها برای کارکنان حوزه سلامتی و تناسب اندام. | نمایش نحوه صحیح کار با تجهیزات تناسب اندام، مانند دستگاه‌های مقاومتی، دستگاه‌های هوازی، وزنه‌های آزاد یا دستگاه‌های ارزیابی آمادگی جسمانی. | طراحی کلاس‌های تناسب اندام یا سلامتی، مانند یوگا، ایروبیک، تمرینات قدرتی یا ورزش‌های آبی، با اطمینان از تنوع کلاس‌های ارائه‌شده. | تدوین کمپین‌های بازاریابی برای ترویج سبک زندگی سالم یا مشارکت در برنامه‌های تناسب اندام و سلامتی. | تدوین یا هماهنگی برنامه‌ها یا خدمات تناسب اندام و سلامتی. | ارزیابی برنامه‌های تناسب اندام و سلامتی برای تعیین میزان اثربخشی آن‌ها. | تفسیر داده‌های بیمه یا داده‌های حساب بازپرداخت سلامت (HRA) برای تدوین برنامه‌هایی که نیازهای خاص جوامع هدف را برطرف کند. | نگهداری تجهیزات یا تأسیسات ورزشی، یا ترتیب دادن نگهداری آن‌ها. | نگهداری برنامه‌های زمانی، سوابق یا گزارش‌های مرتبط با سلامتی و تناسب اندام. | مدیریت یا نظارت بر تأسیسات ورزشی یا تفریحی، با اطمینان از ایمن و پاکیزه بودن تأسیسات و تجهیزات. | سازماندهی و نظارت بر رویدادهایی مانند دوهای همگانی یا پیاده‌روی‌های سازمان‌یافته. | سازماندهی و نظارت بر برنامه‌های تناسب اندام یا سلامتی، مانند ارائه اطلاعات، اهدای خون یا آموزش کمک‌های اولیه و احیای قلبی‌ریوی (CPR). | سازماندهی و نظارت بر غربالگری‌های سلامت یا سایر اقدامات پیشگیرانه، مانند ماموگرافی، غربالگری فشار خون یا کلسترول، یا واکسیناسیون آنفلوانزا. | تهیه یا اجرای بودجه و برنامه‌های راهبردی، عملیاتی، خرید یا نگهداری. | ارائه پشتیبانی یا مشاوره فردی در زمینه سلامت عمومی یا تغذیه. | پیشنهاد یا تأیید برنامه‌ها و خدمات جدید برای ترویج سلامتی و تناسب اندام، ایجاد درآمد یا کاهش هزینه‌ها. | پاسخ‌گویی به درخواست‌های مشتریان، عموم مردم یا رسانه‌ها برای دریافت اطلاعات درباره برنامه‌ها یا خدمات سلامتی. | انتخاب یا سرپرستی پیمانکاران، مانند مجریان رویدادها یا متخصصان حوزه سلامت، تناسب اندام و سلامتی. | سرپرستی متخصصان تناسب اندام یا سلامتی، مانند مربیان ورزشی، متخصصان تغذیه یا مربیان بهداشت. | تدریس کلاس‌های تناسب اندام برای بهبود قدرت، انعطاف‌پذیری، آمادگی قلبی‌عروقی یا آمادگی جسمانی عمومی شرکت‌کنندگان. | ثبت و پیگیری داده‌های حضور، مشارکت یا عملکرد مرتبط با رویدادهای سلامتی. | پیگیری راهبردها و برنامه‌های مهار هزینه برای ارزیابی اثربخشی آن‌ها. | به‌کارگیری مهارت‌های رایانه‌ای و نرم‌افزارها برای مدیریت وب‌سایت‌ها یا پایگاه‌های داده، انتشار خبرنامه یا برگزاری وبینار.</t>
         </is>
       </c>
     </row>
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>نظارت | سخن گفتن | تفکر انتقادی | شنیدن فعال | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش</t>
+          <t>نظارت | سخن گفتن | تفکر انتقادی | گوش دادن فعال | یادگیری فعال | درک مطلب | راهبردهای یادگیری | نگارش</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>امور اداری و دفتری | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری | امور اداری و منابع انسانی | بازاریابی و فروش | اقتصاد و حسابداری</t>
+          <t>اداری | خدمات مشتری و شخصی | مدیریت و اداره | پرسنل و منابع انسانی | فروش و بازاریابی | اقتصاد و حسابداری</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | درک کتبی | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>پیرایشگران مردانه | سرپرستان رده‌اول کارکنان خدمات شخصی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | آرایشگران و متخصصان زیبایی پوست و مو | ماساژورها و ماساژدرمانگران | متخصصان مراقبت از پوست</t>
+          <t>پیرایشگران مردانه | سرپرستان رده‌اول کارکنان خدمات فردی و مراقبتی | مدیران و هماهنگ‌کننده‌های برنامه‌های سلامت و تندرستی | آرایشگران و متخصصان زیبایی | ماساژدرمانگران | متخصصان و تکنسین‌های مراقبت از پوست</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی، هدایت و ارتقای خدمات، دوره‌ها و بسته‌های اسپا | نظارت بر رعایت ضوابط و دستورالعمل‌های بهداشتی و ایمنی | تنظیم بودجه، کنترل هزینه‌ها و ثبت تراکنش‌های مالی روزانه | استخدام، مصاحبه و تعیین وظایف و استانداردهای کاری پرسنل | ارزیابی عملکرد کارکنان و آموزش مهارت‌های فنی و رفتاری | هماهنگی و نظارت بر نوبت‌دهی مراجعان و تقویم کاری پرسنل | نظارت بر عملکرد، تعمیر و نگهداری ابزار و تجهیزات تخصصی | کنترل موجودی مواد اولیه و محصولات و ثبت سفارش‌های خرید | رسیدگی به نظرات، درخواست‌ها و شکایات مراجعان | اجرای راهکارهای بازاریابی و فروش خدمات، محصولات و اشتراک‌ها</t>
+          <t>ارزیابی عملکرد کارکنان و ارائه پیشنهاد برای بهبود کار. | بررسی تجهیزات اسپا برای اطمینان از عملکرد صحیح آن‌ها. | هماهنگی برنامه‌های زمانی مجموعه برای بیشینه‌سازی بهره‌برداری و کارایی. | تدوین یا اجرای راهبردهای بازاریابی. | تعیین اهداف خدماتی یا فروش برای کارکنان و راهنمایی آنان در تحقق این اهداف. | هدایت امور نگهداری یا تعمیر تأسیسات. | تعیین بودجه و اهداف مالی اسپا. | آگاه‌سازی کارکنان از شرح وظایف، انتظارات عملکردی، استانداردهای خدمات به مشتری، یا سیاست‌ها و دستورالعمل‌های سازمانی. | انبارگردانی محصولات و سفارش اقلام جدید. | نگهداری پایگاه‌های داده مشتریان. | پایش عملیات برای اطمینان از رعایت استانداردهای بهداشتی، ایمنی یا نظافتی مربوطه. | شرکت در دوره‌های آموزش مداوم برای به‌روز نگه‌داشتن دانش صنعت. | انجام امور حسابداری، مانند ثبت گردش نقدی روزانه، تهیه اسناد واریز بانکی یا تنظیم صورت‌های مالی. | برنامه‌ریزی یا هدایت خدمات و برنامه‌های اسپا. | جذب، مصاحبه یا استخدام کارکنان. | پاسخ‌گویی به پرسش‌ها یا شکایت‌های مشتریان. | زمان‌بندی نوبت مراجعان. | زمان‌بندی کارکنان یا نظارت بر برنامه‌ریزی زمانی آنان. | فروش محصولات، خدمات یا عضویت‌ها. | آموزش کارکنان در زمینه استفاده یا فروش محصولات، برنامه‌ها یا فعالیت‌ها. | احراز صلاحیت کارکنان، از جمله الزامات تحصیلی و گواهی‌نامه‌ای.</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | امور اداری و منابع انسانی | خدمات مشتریان و خدمات فردی | اقتصاد و حسابداری | رایانه و الکترونیک | حقوق و مقررات دولتی | بازاریابی و فروش</t>
+          <t>مدیریت و اداره | پرسنل و منابع انسانی | خدمات مشتری و شخصی | اقتصاد و حسابداری | رایانه و الکترونیک | قانون و دولت | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات | حساسیت به مسئله</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات | حساسیت به مسئله</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مدیران عامل و مدیران ارشد اجرایی | مدیران کل و مدیران عملیات | مدیران خدمات اداری | مدیران مالی | مدیران منابع انسانی | مدیران بازاریابی | مدیران فروش</t>
+          <t>مدیران عامل و مدیران ارشد اجرایی | مدیران کل و مدیران عملیات | مدیران خدمات اداری و پشتیبانی | مدیران امور مالی | مدیران منابع انسانی | مدیران بازاریابی | مدیران فروش</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی، هدایت و هماهنگی عملیات اجرایی واحدها و بخش‌های سازمانی | تدوین اهداف، برنامه‌های کلان، خط‌مشی‌ها و رویه‌های عملیاتی | سرپرستی، هماهنگی و نظارت بر فعالیت‌های کارکنان تخصصی و اجرایی | تنظیم، دفاع و نظارت بر اجرای بودجه‌های جاری و سرمایه‌ای | تجزیه‌وتحلیل داده‌های عملیاتی و مالی برای سنجش تحقق اهداف | جذب، گزینش، ارزیابی عملکرد و تصمیم‌گیری درباره ارتقای کارکنان | مذاکره، بازبینی و تأیید قراردادها و خریدهای مربوط به کالا و خدمات | حصول اطمینان از انطباق فرایندها با قوانین جاری و خط‌مشی‌های سازمان | رفع مسائل حساس و بحران‌های عملیاتی و حل اختلافات کارکنان و مراجعان | نمایندگی سازمان در تعامل با ذی‌نفعان، تأمین‌کنندگان و مراجع بیرونی</t>
+          <t>برنامه‌ریزی، هدایت و هماهنگی عملیات سازمان‌ها یا واحدهایی که جداگانه طبقه‌بندی نشده‌اند. | تعیین اهداف کلان، اهداف عملیاتی، سیاست‌ها و رویه‌های اجرایی واحد سازمانی. | هدایت و هماهنگی فعالیت‌های کارکنان سرپرست و متخصص. | تهیه، توجیه و اداره بودجه‌های جاری و سرمایه‌ای. | تجزیه و تحلیل داده‌های عملیاتی و مالی برای ارزیابی عملکرد در برابر اهداف. | جذب، استخدام، آموزش و ارزیابی کارکنان و ارائه پیشنهاد درباره اقدامات پرسنلی. | مذاکره و تأیید قراردادها، توافق‌نامه‌ها و خرید کالاها و خدمات. | حصول اطمینان از رعایت قوانین، مقررات و سیاست‌های سازمانی مربوطه. | تهیه گزارش‌ها و ارائه‌ها برای مدیریت ارشد و هیئت‌های حاکمیتی. | شناسایی فرصت‌های بهبود فرایند و اجرای تغییرات برای افزایش کارایی. | رفع مشکلات عملیاتی ارجاع‌شده، مسائل مشتریان و اختلافات کارکنان. | نمایندگی سازمان در تعامل با مشتریان، تأمین‌کنندگان و نهادهای بیرونی. | پایش روندهای صنعت و فعالیت رقبا برای پشتیبانی از تصمیم‌های برنامه‌ریزی. | هدایت تخصیص کارکنان، تجهیزات و امکانات میان پروژه‌ها.</t>
         </is>
       </c>
     </row>
@@ -679,17 +679,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>نگارش | درک مطلب | سخن گفتن | شنیدن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>نگارش | درک مطلب | سخن گفتن | گوش دادن فعال | تفکر انتقادی | نظارت | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>زبان انگلیسی | حقوق و مقررات دولتی | مدیریت و امور اداری | زیست‌شناسی | آموزش و تدریس | امور اداری و دفتری | شیمی</t>
+          <t>زبان انگلیسی | قانون و دولت | مدیریت و اداره | زیست‌شناسی | آموزش و پرورش | اداری | شیمی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | درک کتبی | بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | درک کتبی | بیان شفاهی | درک شفاهی | استدلال قیاسی | حساسیت به مسئله | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مدیران تطبیق و نظارت مقرراتی | کارشناسان امور انطباق مقرراتی | بازرسان انطباق زیست‌محیطی | ممیزان و بازرسان مالی | تحلیل‌گران مدیریت | مدیران سیستم‌های کنترل کیفیت | کارشناسان امور انطباق مقرراتی و حقوقی صنایع</t>
+          <t>مدیران تطبیق و نظارت مقرراتی | کارشناسان پایش انطباق و بازرسی مقرراتی | بازرسان رعایت ضوابط زیست‌محیطی | بازرسان و ارزیابان مالی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران سیستم‌های کنترل کیفیت | کارشناسان امور رگولاتوری و انطباق مقرراتی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>تدوین راهبردها و برنامه‌های اجرایی اخذ مجوز و ثبت محصولات جدید | نظارت بر تهیه، تدوین و ارسال مستندات، پرونده‌ها و گزارش‌ها به مراجع صدور پروانه | بازبینی کلیه اسناد تنظیمی از حیث صحت، کفایت فنی و انطباق با قوانین | ابلاغ الزامات مراجع ذی‌صلاح به واحدهای سازمانی و تفسیر دستورالعمل‌ها | نمایندگی سازمان در تعامل با مراجع قانونی و ناظران ملی و بین‌المللی | تدوین، بازنگری و استقرار روش‌های اجرایی استاندارد (SOP) و شیوه‌نامه‌های کاری | پایش مستمر تغییرات قوانین، بخشنامه‌ها و روندهای مقرراتی حاکم بر صنعت | مدیریت و هماهنگی فرایندهای ممیزی، بازرسی‌های قانونی و فراخوان محصولات | ارائه مشاوره‌های مقرراتی به تیم‌های تحقیق‌وتوسعه، تولید و بازاریابی | آموزش کارکنان درباره خط‌مشی‌ها، آیین‌نامه‌ها و الزامات حقوقی و نظارتی</t>
+          <t>انتقال اطلاعات نظارتی به واحدهای مختلف و حصول اطمینان از تفسیر صحیح این اطلاعات. | مشارکت در تدوین یا اجرای برنامه‌های راهبردی و عملیاتی واحد کسب‌وکار. | هماهنگی فرایندهای کشف اسناد و اخذ اظهارات داخلی با کارکنان واحد حقوقی. | تدوین و نگهداری رویه‌های اجرایی استاندارد یا شیوه‌های کاری محلی. | تدوین راهبردهای نظارتی و برنامه‌های اجرایی برای تهیه و ارائه پرونده محصولات جدید. | برقراری ارتباط با نهادهای نظارتی محیط‌زیستی ایالتی یا فدرال برای آگاهی از پیامدهای احتمالی مقررات پیشنهادی محیط‌زیستی و تحلیل آن‌ها. | هدایت امور مستندسازی برای حصول اطمینان از رعایت مقررات و استانداردهای داخلی و بین‌المللی. | هدایت تهیه و ارائه درخواست‌ها، گزارش‌ها یا مکاتبات مربوط به نهادهای نظارتی. | استقرار رویه‌ها یا سامانه‌هایی برای انتشار اسناد ارسالی به‌صورت چاپی یا الکترونیکی. | تعیین اولویت‌ها یا بودجه امور نظارتی و تخصیص منابع و حجم کار. | ارزیابی سامانه‌های جدید انتشار نرم‌افزاری و رایزنی با نهادهای نظارتی درباره اخبار یا به‌روزرسانی‌های انتشار الکترونیکی اسناد. | ارزیابی جنبه‌های سبز امور نظارتی، مانند استفاده از مواد سمی در بسته‌بندی، مسائل ردپای کربن، یا اجرای سیاست‌های سبز. | تدوین یا اجرای سیاست‌ها و رویه‌های امور نظارتی برای حفظ یا ارتقای انطباق با مقررات. | اجرا یا پایش سامانه‌های رسیدگی به شکایات برای حصول اطمینان از رسیدگی مؤثر و به‌موقع به همه شکایات. | بررسی شکایت‌های مربوط به محصول و تهیه مستندات و پرونده‌های لازم برای ارائه به نهادهای نظارتی ذی‌ربط. | به‌روز نگه‌داشتن دانش مقررات مربوطه، از جمله مقررات پیشنهادی و نهایی. | مدیریت فعالیت‌هایی مانند ممیزی، بازرسی نهادهای نظارتی یا فراخوان جمع‌آوری محصول. | پایش روندهای نوظهور مقررات صنعت برای تعیین پیامدهای احتمالی آن بر فرایندهای سازمان. | پایش فعالیت‌های امور نظارتی برای اطمینان از همسویی آن‌ها با ابتکارهای پایداری یا سبز شرکت. | پایش روندهای امور نظارتی مرتبط با مسائل محیط‌زیستی. | مشارکت در تدوین یا اجرای پروتکل‌های کارآزمایی بالینی. | ارائه راهنمایی نظارتی به واحدها یا تیم‌های پروژه توسعه در زمینه طراحی، توسعه، ارزیابی یا بازاریابی محصولات. | ارائه پاسخ به نهادهای نظارتی درباره اطلاعات یا مسائل محصول. | نمایندگی سازمان نزد نهادهای نظارتی داخلی یا بین‌المللی در موضوعات یا تصمیم‌های مهم سیاستی مرتبط با محصولات شرکت. | بازبینی همه مدارک ارسالی به نهادهای نظارتی برای اطمینان از به‌موقع بودن، دقت، جامعیت یا انطباق با استانداردهای نظارتی. | بازبینی مدارکی مانند ادبیات بازاریابی یا راهنمای کاربر برای اطمینان از رعایت الزامات نهادهای نظارتی. | آموزش کارکنان در زمینه سیاست‌ها یا رویه‌های نظارتی.</t>
         </is>
       </c>
     </row>
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | مدیریت و امور اداری | امور اداری و منابع انسانی | رایانه و الکترونیک | آموزش و تدریس | ایمنی و امنیت عمومی</t>
+          <t>قانون و دولت | مدیریت و اداره | پرسنل و منابع انسانی | رایانه و الکترونیک | آموزش و پرورش | ایمنی و امنیت عمومی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>بیان کتبی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>بیان کتبی | حساسیت به مسئله | بیان شفاهی | درک شفاهی | درک کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کارشناسان امور انطباق مقرراتی | ممیزان و بازرسان مالی | ممیزان، بازرسان و تحلیل‌گران بررسی تقلب | بازرسان و محققان اموال دولتی | تحلیل‌گران مدیریت | مدیران امور انطباق مقرراتی و حقوقی صنایع | مدیران حراست و حفاظت فیزیکی</t>
+          <t>کارشناسان پایش انطباق و بازرسی مقرراتی | بازرسان و ارزیابان مالی | کارشناسان بازرسی، کشف و تحلیل تقلب | بازرسان و ممیزان اموال دولتی | کارشناسان تحلیل مدیریت و روش‌ها | مدیران امور انطباق مقرراتی و حقوقی صنایع | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>برنامه‌ریزی، هدایت و اجرای شیوه‌نامه‌ها و خط‌مشی‌های انطباق مقرراتی در سازمان | طراحی و اجرای نظارت‌های دوره‌ای و ممیزی‌های داخلی انطباق با استانداردها | هدایت تحقیقات و رسیدگی‌های داخلی به تخلفات و انحرافات قانونی و اداری | شناسایی و ارزیابی ریسک‌های عدم انطباق و تدوین راهکارهای کنترل ریسک | نظارت بر سامانه‌های گزارش‌دهی داخلی، سوت‌زنی و پیگیری شکایات | ارائه گزارش‌های عملکردی و تحلیلی وضعیت انطباق به هیئت‌مدیره و مراجع نظارتی | تدوین و اجرای برنامه‌های آموزشی پیرامون قوانین، اخلاق حرفه‌ای و مقررات | بررسی مستندات بازاریابی و قراردادها برای تطابق با قوانین حاکم | همکاری با ممیزان و بازرسان مستقل بیرونی در فرآیندهای حسابرسی و بازرسی | اصلاح و بازنگری رویه‌های سازمانی متناسب با تغییرات مقرراتی و قانونی</t>
+          <t>ارائه مشاوره به مدیریت داخلی یا شرکای تجاری درباره اجرا یا اداره برنامه‌های انطباق. | ارائه مشاوره به متخصصان فنی درباره تدوین یا استفاده از ابزارهای انطباق یا گزارش‌دهی محیط‌زیستی. | همکاری با واحدهای منابع انسانی برای حصول اطمینان از اجرای یکسان راهبردهای اقدام انضباطی در موارد نقض استانداردهای انطباق. | انجام ممیزی‌های محیط‌زیستی برای اطمینان از رعایت استانداردهای محیط‌زیستی. | انجام یا هدایت تحقیقات داخلی درباره مسائل انطباق. | انجام بازبینی‌ها یا ممیزی‌های داخلی دوره‌ای برای اطمینان از رعایت رویه‌های انطباق. | رایزنی با وکلای شرکت در صورت لزوم برای رسیدگی به مسائل دشوار انطباق حقوقی. | طراحی یا اجرای بهبودها در اطلاع‌رسانی، پایش یا اعمال استانداردهای انطباق. | تدوین راهبردهای مدیریت ریسک بر پایه ارزیابی ریسک‌های محصول، انطباق یا عملیات. | هدایت برنامه‌های محیط‌زیستی، مانند انطباق هوا یا آب، مخازن ذخیره روزمینی یا زیرزمینی، پیشگیری یا مهار نشت، مدیریت پسماند یا مواد خطرناک، بازیافت پسماند جامد، مدیریت پسماند پزشکی، کیفیت هوای داخلی، مدیریت تلفیقی آفات، آموزش کارکنان، یا آمادگی در برابر بلایا. | هدایت تدوین یا اجرای سیاست‌ها و رویه‌های مرتبط با انطباق در سراسر سازمان. | بحث درباره مسائل نوظهور انطباق برای حصول اطمینان از آگاهی مدیریت و کارکنان از سامانه‌ها، سیاست‌ها و شیوه‌های گزارش‌دهی انطباق. | انتشار سیاست‌ها و رویه‌های مکتوب مرتبط با فعالیت‌های انطباق. | ارزیابی رویه‌های آزمون برای برآورده کردن مشخصات برنامه‌های پایش محیط‌زیستی. | ارائه گزارش‌های انطباق مقتضی به نهادهای نظارتی. | شناسایی مسائل انطباق که نیازمند پیگیری یا بررسی هستند. | آگاه ماندن از تغییرات، روندها یا بهترین شیوه‌های در پیش روی صنعت. | نگهداری مستندات فعالیت‌های انطباق، مانند شکایت‌های دریافت‌شده یا نتایج بررسی‌ها. | پایش سامانه‌های انطباق برای اطمینان از اثربخشی آن‌ها. | نظارت بر سامانه‌های گزارش‌دهی داخلی، مانند خطوط تلفن گزارش تخلف شرکت. | تهیه گزارش‌های مدیریتی درباره عملیات و پیشرفت امور انطباق. | ارائه کمک به ممیزان داخلی یا خارجی در بازبینی‌های انطباق. | ارائه آموزش به کارکنان در موضوعات، سیاست‌ها یا رویه‌های مرتبط با انطباق. | گزارش موارد نقض استانداردهای انطباق یا مقررات به نهادهای اجرایی دارای صلاحیت، در صورت لزوم یا الزام. | بازبینی اطلاع‌رسانی‌هایی مانند تبلیغات فروش اوراق بهادار برای اطمینان از نبود نقض استانداردها یا مقررات. | بازبینی یا اصلاح سیاست‌ها یا دستورالعمل‌های اجرایی برای انطباق با تغییرات استانداردها یا مقررات محیط‌زیستی. | ایفای نقش به‌عنوان مرجع تماس محرمانه برای کارکنان جهت ارتباط با مدیریت، شفاف‌سازی مسائل یا دوراهی‌ها، یا گزارش تخلفات. | احراز اینکه همه سیاست‌ها و رویه‌های نظارتی مستند، اجرا و اطلاع‌رسانی شده‌اند. | احراز اینکه فناوری نرم‌افزاری لازم برای نظارت و پایش کافی در همه حوزه‌های الزامی مستقر است.</t>
         </is>
       </c>
     </row>
@@ -793,12 +793,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نظارت | نگارش | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ایمنی و امنیت عمومی | حقوق و مقررات دولتی | مدیریت و امور اداری | آموزش و تدریس | روان‌شناسی | رایانه و الکترونیک</t>
+          <t>ایمنی و امنیت عمومی | قانون و دولت | مدیریت و اداره | آموزش و پرورش | روان‌شناسی | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>کارشناسان تداوم کسب‌وکار | مدیران تطبیق و نظارت مقرراتی | سرپرستان رده‌اول نیروهای حراست و انتظامات | ممیزان، بازرسان و تحلیل‌گران بررسی تقلب | کارآگاهان و محققان خصوصی | متخصصان پیشگیری از کسری و هدررفت کالا | مدیران حراست و حفاظت فیزیکی</t>
+          <t>کارشناسان برنامه‌ریزی تداوم کسب‌وکار | مدیران تطبیق و نظارت مقرراتی | سرپرستان رده‌اول کارکنان حراست و انتظامات | کارشناسان بازرسی، کشف و تحلیل تقلب | کارآگاهان و بازرسان خصوصی | کارشناسان پیشگیری از سرقت و افت کالا در خرده‌فروشی‌ها | مدیران حراست و انتظامات</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>تدوین و اجرای برنامه‌ها و دستورالعمل‌های کاهش ضایعات و صیانت از کالا | ارزیابی ریسک‌های امنیتی شعب و انبارها و تخصیص نیروها و تجهیزات لازم | هدایت تحقیقات داخلی درباره سرقت‌های اداری، تبانی، تقلب و تخلفات | همکاری با نهادهای انتظامی و قضایی برای پیگیری پرونده‌های سرقت و جعل | نظارت بر نصب، کارکرد و نگهداری سیستم‌های نظارت تصویری و دزدگیرها | تحلیل داده‌های انبار و فروش برای شناسایی مغایرت‌ها و الگوهای کسری | برنامه‌ریزی و هدایت ممیزی‌های ایمنی، انبارگردانی و مغایرت‌های مالی | بازرسی‌های سرزده و دوره‌ای از فروشگاه‌ها و مراکز توزیع | تدوین و اجرای دوره‌های آموزشی پیشگیری از زیان و کنترل موجودی برای کارکنان | مدیریت شرایط بحرانی نظیر خشونت در محیط کار و سرقت‌های سازمان‌یافته</t>
+          <t>اداره سامانه‌ها و برنامه‌های کاهش زیان، کنترل موجودی یا افزایش ایمنی. | ارائه مشاوره به واحدهای خرده‌فروشی درباره تدوین رویه‌های بررسی زیان. | ارائه مشاوره به مدیران خرده‌فروشی درباره رعایت آیین‌نامه‌ها، قوانین، مقررات یا استانداردهای مربوطه. | تجزیه و تحلیل داده‌های خرده‌فروشی برای شناسایی روندهای جاری یا نوظهور سرقت و تقلب. | ارزیابی نیازهای امنیتی در همه شعب برای اطمینان از استقرار درست منابع پیشگیری از زیان، مانند نیروی انسانی و فناوری. | همکاری با نیروهای انتظامی برای بررسی و حل پرونده‌های سرقت یا تقلب بیرونی. | هماهنگی یا انجام تحقیقات داخلی درباره مشکلاتی مانند سرقت کارکنان و نقض سیاست‌های پیشگیری از زیان شرکت. | هماهنگی تحقیقات سرقت و تقلب مرتبط با مجرمان حرفه‌ای یا فعالیت‌های گروهی سازمان‌یافته. | ایجاد و حفظ همکاری با نهادهای انتظامی فدرال، ایالتی یا محلی یا اعضای جامعه پیشگیری از زیان در خرده‌فروشی. | هدایت نصب تجهیزات نظارت پنهان، مانند دوربین‌های امنیتی. | هدایت برنامه‌های ممیزی پیشگیری از زیان، شامل ممیزی فروشگاه‌های هدف، ممیزی نگهداری، ممیزی ایمنی یا ممیزی سامانه‌های الکترونیکی نظارت بر کالا (EAS). | استخدام یا سرپرستی کارکنان پیشگیری از زیان. | شناسایی احتمال بروز زیان و تدوین راهبردهایی برای حذف آن. | بررسی یا مصاحبه با افراد مظنون به سرقت از فروشگاه یا سرقت داخلی. | نگهداری پایگاه‌های داده مانند سوابق چک‌های برگشتی، گزارش‌های متخلفان مکرر و فهرست فعال‌سازی آژیرها. | نگهداری مستندات همه فعالیت‌های پیشگیری از زیان. | پایش و بازبینی رویه‌ها و سامانه‌های اسناد اداری برای پیشگیری از کسری‌های ناشی از خطا. | پایش رعایت رویه‌های عملیاتی، ایمنی یا کنترل موجودی، از جمله استانداردهای امنیت فیزیکی. | انجام ممیزی وجه نقد و بررسی واریزها برای احراز کامل موجودی نقدی فروشگاه. | انجام یا هدایت بررسی موجودی در پاسخ به نتایج کسری خارج از دامنه قابل قبول. | ارائه توصیه‌ها و راهکارها در وضعیت‌های بحرانی مانند خشونت در محل کار، اعتراض‌ها و تجمعات. | پیشنهاد بهبود در برنامه‌ها، نیروی انسانی، زمان‌بندی یا آموزش پیشگیری از زیان. | بازبینی گزارش‌های استثنای پیشگیری از زیان و مغایرت‌های نقدی برای اطمینان از رعایت دستورالعمل‌ها. | سرپرستی امور نظارت تصویری، کشف یا رسیدگی کیفری مرتبط با پرونده‌های سرقت و جرم. | آموزش کارکنان پیشگیری از زیان، مدیران خرده‌فروشی یا کارکنان فروشگاه در زمینه اقدامات کنترل و پیشگیری از زیان. | احراز استفاده و نگهداری صحیح سامانه‌های امنیت فیزیکی، مانند دوربین مدار بسته، برچسب‌های کالا و آژیرهای سرقت. | بازدید از فروشگاه‌ها برای اطمینان از رعایت سیاست‌ها و رویه‌های شرکت.</t>
         </is>
       </c>
     </row>
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | ریاضیات | راهبردهای یادگیری | یادگیری فعال</t>
+          <t>گوش دادن فعال | درک مطلب | سخن گفتن | تفکر انتقادی | نظارت | نگارش | ریاضیات | راهبردهای یادگیری | یادگیری فعال</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | مکانیک | فنی و مهندسی | ایمنی و امنیت عمومی | امور اداری و منابع انسانی | رایانه و الکترونیک | تولید و فراوری</t>
+          <t>مدیریت و اداره | مکانیک | مهندسی و فناوری | ایمنی و امنیت عمومی | پرسنل و منابع انسانی | رایانه و الکترونیک | تولید و فرآوری</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | مرتب‌سازی اطلاعات | استدلال قیاسی | استدلال استقرایی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | ترتیب‌دهی اطلاعات | استدلال قیاسی | استدلال استقرایی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید صنعتی | متصدیان اتاق کنترل نیروگاه | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی بادی | تکنسین‌های خدمات و تعمیرات توربین‌های بادی</t>
+          <t>مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مدیران تولید صنعتی | اپراتورهای نیروگاه برق | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد | تکنسین‌های تعمیر و نگهداری توربین‌های بادی</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>تدوین دستورالعمل‌های بهره‌برداری و انتقال از فاز ساخت به فاز تجاری | نظارت بر عملیات نگهداری پیشگیرانه و تعمیرات توربین‌ها، پست‌ها و خطوط انتقال | نظارت بر رعایت کامل ضوابط ایمنی، بهداشت کار و الزامات زیست‌محیطی | پایش مستمر شاخص‌های عملکردی سایت، ضریب دسترسی و کاهش توقفات فنی | تدوین و مدیریت بودجه‌های عملیاتی، تعمیراتی و برآورد هزینه‌ها | سرپرستی، ارزیابی و آموزش مستمر تکنسین‌ها و پیمانکاران فنی | تأمین قطعات یدکی حیاتی، ابزارآلات و تجهیزات موردنیاز مزرعه بادی | رسیدگی به تعهدات گارانتی، پیگیری دعاوی فنی و عیب‌یابی تجهیزات اصلی | هماهنگی و مذاکره با کارفرما، شبکه دیسپاچینگ برق و پیمانکاران جانبی | ثبت دقیق سوابق تعمیراتی، سفارش‌های کاری و گزارش‌های توقف نیروگاه</t>
+          <t>تدوین فرایندها یا رویه‌های عملیات بادی، از جمله گذار از مرحله ساخت به بهره‌برداری تجاری. | ایجاد ارتباط و تعامل با مشتریان، مدیران سایت، توسعه‌دهندگان، مالکان زمین، مقامات، نمایندگان شرکت‌های خدمات عمومی یا ساکنان محلی. | تعیین اهداف کلان، اهداف عملیاتی یا اولویت‌های عملیات مزرعه بادی. | برآورد هزینه‌های مرتبط با بهره‌برداری، از جمله تعمیرات یا نگهداری پیشگیرانه. | نگهداری سوابق عملیاتی، مانند دستور کارها، فرم‌های بازرسی سایت یا سایر مستندات. | مدیریت خدمات تعمیر یا تعویض در دوره ضمانت. | پایش و نگهداری سوابق عملیات روزانه تأسیسات. | سفارش قطعات، ابزار یا تجهیزات لازم برای نگهداری، بازیابی یا بهبود عملیات مزرعه بادی. | نظارت بر نگهداری تجهیزات یا سازه‌های مزرعه بادی، مانند برج‌ها، ترانسفورماتورها، سامانه‌های جمع‌آوری برق، جاده‌های دسترسی یا سایر دارایی‌های سایت. | تهیه بودجه عملیاتی مزرعه بادی. | ارائه پشتیبانی فنی به مشتریان، کارکنان یا پیمانکاران فرعی مزرعه بادی. | جذب یا انتخاب کارکنان، پیمانکاران یا پیمانکاران فرعی عملیات بادی. | بازبینی، مذاکره یا تأیید قراردادهای مزرعه بادی. | سرپرستی کارکنان یا پیمانکاران فرعی برای اطمینان از کیفیت کار یا رعایت مقررات و سیاست‌های ایمنی. | ثبت و نگهداری سوابق عملیات بادی، مانند عملکرد سایت، رویدادهای توقف، مصرف قطعات یا رویدادهای پست برق. | آموزش کارکنان یا هماهنگی آموزش آنان در زمینه عملیات، ایمنی، مسائل محیط‌زیستی یا مسائل فنی.</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | شنیدن فعال | نظارت | یادگیری فعال | ریاضیات</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | گوش دادن فعال | نظارت | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مدیریت و امور اداری | ساختمان و ساخت‌وساز | فنی و مهندسی | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
+          <t>مدیریت و اداره | ساختمان و ساخت‌وساز | مهندسی و فناوری | اقتصاد و حسابداری | ریاضیات | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | مرتب‌سازی اطلاعات</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | حساسیت به مسئله | بیان کتبی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران فنی و مهندسی و معماری | مهندسان عمران | مدیران طرح‌های ساختمانی و عمرانی | ممیزان انرژی | کارشناسان مدیریت پروژه | مهندسان انرژی بادی | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی</t>
+          <t>مدیران فنی و مهندسی و معماری | مهندسان عمران | مدیران پروژه‌های ساختمانی | ممیزان انرژی | کارشناسان مدیریت پروژه | مهندسان انرژی باد | مدیران بهره‌برداری و تعمیرات نیروگاه‌های بادی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>تدوین برنامه جامع پروژه مشتمل بر محدوده، اهداف، منابع، زمان‌بندی و بودجه | مدیریت مطالعات پتانسیل‌سنجی باد و ارزیابی‌های زیست‌محیطی سایت‌های احداث | تهیه، تنظیم و پیگیری مدارک اخذ پروانه‌ها و مجوزهای قانونی ساخت و بهره‌برداری | مذاکره و تنظیم قراردادهای اتصال به شبکه، خرید تضمینی برق (PPA) و تملک اراضی | تهیه اسناد مناقصه (RFP) برای احداث نیروگاه و خرید تجهیزات توربین‌ها | ارزیابی پیشنهادها و پروپوزال‌های فنی و مالی ارائه‌شده در مناقصات | کنترل هزینه‌های طرح متناسب با بودجه مصوب و پیش‌بینی جریانات نقدی | نظارت بر عملکرد مشاوران و پیمانکاران مهندسی و عمرانی در فاز اجرا | بررسی اسناد فنی مهندسی و نقشه‌ها جهت تطابق با استانداردها و آیین‌نامه‌ها | ارائه گزارش‌های دوره‌ای از پیشرفت فیزیکی و مالی طرح به ذی‌نفعان و سرمایه‌گذاران</t>
+          <t>هماهنگی یا هدایت فعالیت‌های توسعه، ارزیابی انرژی، مهندسی یا ساخت برای اطمینان از تحقق نیازها و اهداف پروژه بادی. | تدوین برنامه‌های پروژه انرژی بادی، شامل دامنه پروژه، اهداف، وظایف، منابع، زمان‌بندی، هزینه‌ها، پیشامدهای احتمالی یا سایر اطلاعات پروژه. | تدوین شرح کار برای بخش‌های پروژه بادی، مانند طراحی، ارزیابی سایت، مطالعات محیط‌زیستی، نقشه‌برداری یا خدمات پشتیبانی میدانی. | راهبری یا پشتیبانی مذاکرات مربوط به توافق‌ها یا معافیت‌های مالیاتی، قراردادهای خرید برق، کاربری زمین یا توافق‌های اتصال به شبکه. | مدیریت ارزیابی‌های سایت یا مطالعات محیط‌زیستی مزارع بادی. | مدیریت هزینه‌های پروژه بادی برای ماندن در چارچوب بودجه. | تهیه یا کمک به تهیه درخواست مجوزهای محیط‌زیستی، ساختمانی یا سایر مجوزهای لازم. | تهیه درخواست پیشنهاد (RFP) برای ساخت پروژه بادی یا تأمین تجهیزات. | تهیه مستندات پروژه بادی، از جمله نمودارها یا نقشه‌های چیدمان. | ارائه پشتیبانی فنی برای طراحی، ساخت یا راه‌اندازی پروژه‌های مزرعه بادی. | ارائه گزارش‌های شفاهی یا کتبی وضعیت پروژه به تیم‌های پروژه، مدیریت، پیمانکاران فرعی، مشتریان یا مالکان. | بازبینی مستندات فنی طراحی عمرانی، مهندسی یا ساخت برای اطمینان از انطباق با آیین‌نامه‌ها، استانداردها، الزامات یا مقررات دولتی یا صنعتی مربوطه. | بازبینی یا ارزیابی پیشنهادها یا مناقصه‌ها برای ارائه توصیه درباره واگذاری قراردادها. | سرپرستی کار پیمانکاران فرعی یا مشاوران برای اطمینان از کیفیت و انطباق با مشخصات یا بودجه. | به‌روزرسانی زمان‌بندی‌ها، برآوردها، پیش‌بینی‌ها یا بودجه پروژه‌های بادی.</t>
         </is>
       </c>
     </row>
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | شنیدن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | علوم تجربی و آزمایشگاهی</t>
+          <t>نظارت | تفکر انتقادی | سخن گفتن | درک مطلب | گوش دادن فعال | نگارش | ریاضیات | یادگیری فعال | راهبردهای یادگیری | علوم</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>حقوق و مقررات دولتی | مدیریت و امور اداری | ریاضیات | شیمی | فنی و مهندسی | زیست‌شناسی</t>
+          <t>قانون و دولت | مدیریت و اداره | ریاضیات | شیمی | مهندسی و فناوری | زیست‌شناسی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | مرتب‌سازی اطلاعات</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | ترتیب‌دهی اطلاعات</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان عمران | بازرسان انطباق زیست‌محیطی | مهندسان محیط‌زیست | برنامه‌ریزان احیا و بازیابی زیست‌محیطی | متخصصان و کارشناسان محیط‌زیست، از جمله بهداشت | بوم‌شناسان صنعتی | برنامه‌ریزان شهری و منطقه‌ای</t>
+          <t>مهندسان عمران | بازرسان رعایت ضوابط زیست‌محیطی | مهندسان محیط‌زیست | برنامه‌ریزان احیای محیط زیست | کارشناسان و متخصصان علوم محیطی (شامل بهداشت) | بوم‌شناسان صنعتی | برنامه‌ریزان شهری و منطقه‌ای</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>انجام مطالعات امکان‌سنجی فنی و تحلیل‌های هزینه-فایده پروژه‌های اصلاح زیست‌محیطی | ارزیابی کمی و کیفی مخاطرات آلودگی خاک، آب و هوا بر سلامت انسان و محیط | برنامه‌ریزی و نظارت بر عملیات پاک‌سازی سایت مطابق با الزامات و استانداردهای قانونی | طراحی و نظارت بر اجرای طرح‌های تصفیه و پالایش منابع آب سطحی و زیرزمینی | نظارت فنی بر عملیات تخریب ایمن سازه‌ها و جمع‌آوری پسماندهای ساختمانی | هماهنگی و نظارت بر فرآیندهای بی‌خطرسازی و دفن پسماندهای ویژه و خطرناک | برآورد هزینه‌ها، کنترل بودجه و جذب منابع مالی برای پروژه‌های بازسازی اراضی | بازرسی‌های میدانی از کارگاه‌ها جهت سنجش انتشار آلودگی و پایش پیشرفت عملیات | تهیه اسناد فنی، گزارش‌های ممیزی و پیگیری اخذ مجوزهای قانونی از مراجع ذی‌صلاح | مذاکره و انعقاد قرارداد با پیمانکاران تخصصی تصفیه، خاک‌برداری و دفع ضایعات</t>
+          <t>انجام مطالعات امکان‌سنجی یا هزینه‌فایده برای پروژه‌های پاک‌سازی محیط‌زیستی. | انجام ارزیابی‌های کمّی ریسک برای سلامت انسان، محیط‌زیست یا سایر مخاطرات. | هماهنگی فعالیت‌های میدانی پروژه‌های پاک‌سازی یا احیای محیط‌زیستی برای اطمینان از رعایت قوانین، استانداردها، مقررات یا سایر الزامات محیط‌زیستی. | هماهنگی دفع پسماند خطرناک. | طراحی یا انجام مطالعات احیای محیط‌زیست. | طراحی یا اجرای اقداماتی برای بهبود کیفیت آب، هوا و خاک محل‌های آزمایش نظامی، اراضی معدنی متروکه یا سایر محل‌های آلوده. | طراحی یا اجرای برنامه‌های تخریب سازه‌ای و برداشت نخاله. | طراحی یا اجرای برنامه‌های پاک‌سازی آب‌های سطحی یا زیرزمینی. | تدوین یا اجرای برنامه‌های بازگرداندن پوشش گیاهی در اراضی قهوه‌ای (آلوده متروکه). | تدوین یا اجرای برنامه‌های بازآفرینی پایدار اراضی قهوه‌ای برای اطمینان از احیای پهنه گسترده‌تر از راه حفاظت محیط‌زیستی یا ایجاد منافع اقتصادی و اجتماعی. | برآورد هزینه‌های پاک‌سازی و احیای محیط‌زیستی پروژه‌های بازتوسعه اراضی. | شناسایی منابع تأمین مالی پروژه و درخواست آن. | شناسایی منابع آلودگی محیط‌زیستی. | بازرسی محل‌ها برای ارزیابی آسیب محیط‌زیستی یا پایش پیشرفت پاک‌سازی. | نگهداری سوابق تصمیم‌ها، اقدامات و پیشرفت پروژه‌های بازتوسعه محیط‌زیستی. | مذاکره درباره قراردادهای خدمات یا مواد مورد نیاز پاک‌سازی محیط‌زیستی. | برنامه‌ریزی یا اجرای پروژه‌های بازتوسعه اراضی قهوه‌ای برای تضمین ایمنی، کیفیت و انطباق با استانداردها یا الزامات مربوطه. | تهیه و ارائه درخواست مجوز برای پروژه‌های تخریب، پاک‌سازی، احیا یا ساخت. | تهیه گزارش‌ها یا ارائه‌ها برای انتقال نیازها، وضعیت یا پیشرفت بازتوسعه اراضی قهوه‌ای. | ارائه شهادت کارشناسی در موضوعاتی مانند آلودگی خاک، هوا یا آب و اقدامات پاک‌سازی مرتبط با آن. | ارائه آموزش درباره رویه‌ها و فناوری‌های پاک‌سازی مواد یا پسماند خطرناک. | بازبینی یا ارزیابی طرح‌های تأسیسات تصفیه یا دفع آلاینده‌ها. | بازبینی یا ارزیابی پیشنهادهای پروژه پاک‌سازی محیط‌زیستی.</t>
         </is>
       </c>
     </row>
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>سخن گفتن | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
+          <t>سخن گفتن | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>خدمات مشتریان و خدمات فردی | بازاریابی و فروش | مدیریت و امور اداری | هنرهای تجسمی و نمایشی | ارتباطات و رسانه | امور اداری و دفتری</t>
+          <t>خدمات مشتری و شخصی | فروش و بازاریابی | مدیریت و اداره | هنرهای زیبا | ارتباطات و رسانه | اداری</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | سیالی ذهنی</t>
+          <t>بیان شفاهی | درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بیان کتبی | روانی ایده‌ها</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران تبلیغات و روابط تجاری | مدیران هنری | مدیران جذب منابع و حامیان مالی | هماهنگ‌کنندگان همایش‌ها، کنفرانس‌ها و رویدادها | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | مسئولان انتخاب بازیگر و استعدادیابی</t>
+          <t>مدیران تبلیغات و روابط ترویجی | مدیران هنری | مدیران جذب منابع مالی و حامیان | کارشناسان برنامه‌ریزی و برگزاری همایش‌ها و رویدادها | تهیه‌کنندگان و کارگردانان | مدیران روابط عمومی | مسئولان انتخاب بازیگر و استعدادیابی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>مذاکره با کارفرمایان، تهیه‌کنندگان، باشگاه‌ها و نهادهای صنفی درباره تعهدات قراردادی موکلان | بازاریابی، توسعه برند شخصی و تدوین راهبردهای موفقیت حرفه‌ای برای موکلان | مدیریت امور مالی، مالیاتی و تجاری موکلان از جمله قراردادهای اسپانسری و تبلیغاتی | هماهنگی و برنامه‌ریزی جلسات، اجراها، رویدادها، نشست‌های تبلیغاتی و تقویم کاری | هماهنگی محل اقامت، امور سفر، تشریفات و تأمین نیازمندی‌های رفاهی موکلان | پیگیری وصول دستمزدها، مطالبات مالی، کارمزدها و حق‌الوکاله‌ها طبق قرارداد | ارسال نمونه آثار، رزومه و اقلام تبلیغاتی برای جلب حامیان مالی و فرصت‌های جدید | بررسی و اعتبارسنجی مکان‌های اجرا، تجهیزات فنی و استانداردهای سالن‌ها و اماکن | انجام مصاحبه‌ها و آزمون‌های استعدادیابی جهت ارزیابی و پذیرش موکلان جدید | پیگیری وضعیت قراردادها، روند بازار و فرصت‌های جدید حوزه ورزش و هنر</t>
+          <t>ارائه مشاوره به مشتریان در امور مالی و حقوقی، مانند سرمایه‌گذاری و مالیات. | ترتیب دادن جلسات درباره موضوعات مرتبط با مشتریان. | دریافت حق‌الزحمه، کارمزد یا سایر پرداخت‌ها، بر پایه شرایط قرارداد. | برگزاری آزمون هنری یا مصاحبه برای ارزیابی مشتریان بالقوه. | رایزنی با مشتریان برای تدوین راهبردهای شغلی آنان و تشریح اقدامات انجام‌شده از سوی ایشان. | ایجاد ارتباط با افراد و سازمان‌ها و به‌کارگیری راهبردها و فنون مؤثر برای تضمین موفقیت مشتریان. | به‌کارگیری مربیان یا مدرسان برای مشاوره به مشتریان در موضوعات اجرایی، مانند فنون تمرین یا شیوه ارائه اجرا. | آگاه ماندن از روندها و معاملات صنعت. | مدیریت امور تجاری و مالی مشتریان، مانند ترتیب دادن سفر و اقامت، فروش بلیت و هدایت فعالیت‌های بازاریابی و تبلیغات. | مذاکره با مدیران، برگزارکنندگان، مقامات صنفی و سایر افراد درباره حقوق و تعهدات قراردادی مشتریان. | کسب اطلاعات درباره امکانات، تجهیزات و محل اقامت مربوط به اجرا یا بازرسی آن‌ها برای اطمینان از انطباق با مشخصات. | تهیه صورت‌حساب‌های دوره‌ای برای مشتریان. | زمان‌بندی برنامه‌های تبلیغاتی یا اجرایی مشتریان. | ارسال نمونه آثار مشتریان و سایر مواد تبلیغاتی به کارفرمایان بالقوه برای دریافت فرصت آزمون هنری، حمایت مالی یا قرارداد تبلیغاتی.</t>
         </is>
       </c>
     </row>
